--- a/dataset_t6_grouped/results2/G4/G4_T3269_W0023F0003T0006Z000C1N30_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3269_W0023F0003T0006Z000C1N30_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>42.73472225568345</v>
+        <v>6.944392366548561</v>
       </c>
       <c r="D2" t="n">
-        <v>42.18628901208239</v>
+        <v>6.855271964463388</v>
       </c>
       <c r="E2" t="n">
-        <v>12.07096815022084</v>
+        <v>1.961532324410886</v>
       </c>
       <c r="F2" t="n">
-        <v>11.77419058105551</v>
+        <v>1.91330596942152</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>40.99749415171785</v>
+        <v>6.66209279965415</v>
       </c>
       <c r="D3" t="n">
-        <v>40.21330339671344</v>
+        <v>6.534661801965933</v>
       </c>
       <c r="E3" t="n">
-        <v>12.07096815022084</v>
+        <v>1.961532324410886</v>
       </c>
       <c r="F3" t="n">
-        <v>11.77419058105551</v>
+        <v>1.91330596942152</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>22.58681710571028</v>
+        <v>3.67035777967792</v>
       </c>
       <c r="D4" t="n">
-        <v>22.73268575785188</v>
+        <v>3.69406143565093</v>
       </c>
       <c r="E4" t="n">
-        <v>12.07096815022084</v>
+        <v>1.961532324410886</v>
       </c>
       <c r="F4" t="n">
-        <v>11.77419058105551</v>
+        <v>1.91330596942152</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>34.69872516954889</v>
+        <v>5.638542840051695</v>
       </c>
       <c r="D5" t="n">
-        <v>33.95432183685982</v>
+        <v>5.517577298489721</v>
       </c>
       <c r="E5" t="n">
-        <v>12.07096815022084</v>
+        <v>1.961532324410886</v>
       </c>
       <c r="F5" t="n">
-        <v>11.77419058105551</v>
+        <v>1.91330596942152</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>14.4474816360272</v>
+        <v>2.34771576585442</v>
       </c>
       <c r="D6" t="n">
-        <v>15.04444696436126</v>
+        <v>2.444722631708705</v>
       </c>
       <c r="E6" t="n">
-        <v>12.07096815022084</v>
+        <v>1.961532324410886</v>
       </c>
       <c r="F6" t="n">
-        <v>11.77419058105551</v>
+        <v>1.91330596942152</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>47.0889086935285</v>
+        <v>7.65194766269838</v>
       </c>
       <c r="D7" t="n">
-        <v>46.41738868887038</v>
+        <v>7.542825661941437</v>
       </c>
       <c r="E7" t="n">
-        <v>12.07096815022084</v>
+        <v>1.961532324410886</v>
       </c>
       <c r="F7" t="n">
-        <v>11.77419058105551</v>
+        <v>1.91330596942152</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>27.11196695898587</v>
+        <v>4.405694630835204</v>
       </c>
       <c r="D8" t="n">
-        <v>26.76629668780029</v>
+        <v>4.349523211767548</v>
       </c>
       <c r="E8" t="n">
-        <v>12.07096815022084</v>
+        <v>1.961532324410886</v>
       </c>
       <c r="F8" t="n">
-        <v>11.77419058105551</v>
+        <v>1.91330596942152</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>25.32871367380346</v>
+        <v>4.115915971993061</v>
       </c>
       <c r="D9" t="n">
-        <v>25.53897472930769</v>
+        <v>4.150083393512499</v>
       </c>
       <c r="E9" t="n">
-        <v>12.07096815022084</v>
+        <v>1.961532324410886</v>
       </c>
       <c r="F9" t="n">
-        <v>11.77419058105551</v>
+        <v>1.91330596942152</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>11.75344255354492</v>
+        <v>1.909934414951049</v>
       </c>
       <c r="D10" t="n">
-        <v>11.6651707227283</v>
+        <v>1.895590242443349</v>
       </c>
       <c r="E10" t="n">
-        <v>12.07096815022084</v>
+        <v>1.961532324410886</v>
       </c>
       <c r="F10" t="n">
-        <v>11.77419058105551</v>
+        <v>1.91330596942152</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>14.69078306487509</v>
+        <v>2.387252248042202</v>
       </c>
       <c r="D11" t="n">
-        <v>14.16442970793483</v>
+        <v>2.30171982753941</v>
       </c>
       <c r="E11" t="n">
-        <v>12.07096815022084</v>
+        <v>1.961532324410886</v>
       </c>
       <c r="F11" t="n">
-        <v>11.77419058105551</v>
+        <v>1.91330596942152</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
